--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
-  <si>
-    <t>核对周期</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+  <si>
+    <t>月份</t>
   </si>
   <si>
     <t>业务单号</t>
@@ -86,6 +86,9 @@
     <t>期末在途(调整后)</t>
   </si>
   <si>
+    <t>调整原因</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -144,6 +147,9 @@
   </si>
   <si>
     <t>{.afterEndPeriodTransitQty}</t>
+  </si>
+  <si>
+    <t>{.adjustReason}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1336,13 +1342,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="20" width="30" customWidth="1"/>
+    <col min="1" max="21" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:20">
+    <row r="1" ht="15" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1403,67 +1409,73 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="21300" windowHeight="11265"/>
   </bookViews>
   <sheets>
     <sheet name="平台在途报表" sheetId="1" r:id="rId1"/>
@@ -104,7 +104,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.platformSkuNo}</t>
+    <t>{.skuNo}</t>
   </si>
   <si>
     <t>{.warehouseName}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21300" windowHeight="11265"/>
+    <workbookView windowWidth="25395" windowHeight="7095"/>
   </bookViews>
   <sheets>
     <sheet name="平台在途报表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>月份</t>
   </si>
@@ -38,7 +38,13 @@
     <t>店铺/客户</t>
   </si>
   <si>
-    <t>产品信息</t>
+    <t>ASIN</t>
+  </si>
+  <si>
+    <t>MSKU</t>
+  </si>
+  <si>
+    <t>FNSKU</t>
   </si>
   <si>
     <t>系统SKU</t>
@@ -101,7 +107,13 @@
     <t>{.customerName}</t>
   </si>
   <si>
-    <t>{.productName}</t>
+    <t>{.platformSpuNo}</t>
+  </si>
+  <si>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.platformStockSku}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1342,13 +1354,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="21" width="30" customWidth="1"/>
+    <col min="1" max="23" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:21">
+    <row r="1" ht="15" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1412,70 +1424,82 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="T2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="U2" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="V2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
@@ -104,7 +104,7 @@
     <t>{.shipmentCode}</t>
   </si>
   <si>
-    <t>{.customerName}</t>
+    <t>{.shopName}</t>
   </si>
   <si>
     <t>{.platformSpuNo}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25395" windowHeight="7095"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="平台在途报表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>月份</t>
   </si>
@@ -53,6 +53,9 @@
     <t>仓库</t>
   </si>
   <si>
+    <t>在途仓库</t>
+  </si>
+  <si>
     <t>业务状态</t>
   </si>
   <si>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.intransitWarehouseName}</t>
   </si>
   <si>
     <t>{.shipmentStatus}</t>
@@ -1354,13 +1360,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="23" width="30" customWidth="1"/>
+    <col min="1" max="24" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:23">
+    <row r="1" ht="15" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1430,76 +1436,82 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="X2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpFirstMileInTransitDiff.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>月份</t>
   </si>
@@ -98,6 +98,12 @@
     <t>调整原因</t>
   </si>
   <si>
+    <t>执行状态</t>
+  </si>
+  <si>
+    <t>执行完成时间</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -168,6 +174,12 @@
   </si>
   <si>
     <t>{.adjustReason}</t>
+  </si>
+  <si>
+    <t>{.execStatusName}</t>
+  </si>
+  <si>
+    <t>{.finishTime}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -1360,13 +1372,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="24" width="30" customWidth="1"/>
+    <col min="1" max="26" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:24">
+    <row r="1" ht="15" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1439,79 +1451,91 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="V2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
